--- a/laporan_padel_dki_jakarta_2026-10-04.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-04.xlsx
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp3.075.000</t>
+          <t>Rp3.225.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>68</v>
       </c>
       <c r="D26" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp750.000</t>
+          <t>Rp625.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1691,16 +1691,16 @@
         <v>54</v>
       </c>
       <c r="D41" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp1.863.000</t>
+          <t>Rp2.061.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1877,16 +1877,16 @@
         <v>54</v>
       </c>
       <c r="D47" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp930.000</t>
+          <t>Rp1.000.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2156,16 +2156,16 @@
         <v>17</v>
       </c>
       <c r="D56" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp894.000</t>
+          <t>Rp1.043.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>32</v>
       </c>
       <c r="D59" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp2.025.000</t>
+          <t>Rp2.475.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2621,16 +2621,16 @@
         <v>96</v>
       </c>
       <c r="D71" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp830.000</t>
+          <t>Rp150.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2683,16 +2683,16 @@
         <v>72</v>
       </c>
       <c r="D73" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp2.515.000</t>
+          <t>Rp2.365.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2776,16 +2776,16 @@
         <v>98</v>
       </c>
       <c r="D76" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>12.2%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp2.270.000</t>
+          <t>Rp2.620.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>120</v>
       </c>
       <c r="D78" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp15.155.000</t>
+          <t>Rp14.375.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3086,16 +3086,16 @@
         <v>96</v>
       </c>
       <c r="D86" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rp2.850.000</t>
+          <t>Rp4.050.000</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3633,16 +3633,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp3.890.000</t>
+          <t>Rp4.668.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3850,16 +3850,16 @@
         <v>15</v>
       </c>
       <c r="D11" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp525.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -3881,16 +3881,16 @@
         <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp11.980.000</t>
+          <t>Rp12.375.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -3943,16 +3943,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp2.396.000</t>
+          <t>Rp2.796.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>65</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp6.390.000</t>
+          <t>Rp7.380.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4966,16 +4966,16 @@
         <v>32</v>
       </c>
       <c r="D47" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp1.000.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -4997,16 +4997,16 @@
         <v>80</v>
       </c>
       <c r="D48" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp4.400.000</t>
+          <t>Rp4.800.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5059,16 +5059,16 @@
         <v>72</v>
       </c>
       <c r="D50" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp4.378.000</t>
+          <t>Rp4.577.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>60</v>
       </c>
       <c r="D52" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp5.950.000</t>
+          <t>Rp5.250.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5192,7 +5192,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp10.340.000</t>
+          <t>Rp10.230.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5823,16 +5823,16 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp1.625.000</t>
+          <t>Rp1.750.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -5854,16 +5854,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>36.3%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp9.250.000</t>
+          <t>Rp9.500.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp4.050.000</t>
+          <t>Rp4.550.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6009,16 +6009,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp5.400.000</t>
+          <t>Rp5.850.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6401,16 +6401,16 @@
         <v>200</v>
       </c>
       <c r="D2" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>19.5%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp13.070.000</t>
+          <t>Rp13.370.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6463,16 +6463,16 @@
         <v>74</v>
       </c>
       <c r="D4" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>60.8%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp10.890.000</t>
+          <t>Rp11.170.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6525,16 +6525,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp15.515.000</t>
+          <t>Rp16.595.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp900.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rp200.000</t>
+          <t>Rp150.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -6835,16 +6835,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp3.650.000</t>
+          <t>Rp3.800.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp18.500.000</t>
+          <t>Rp18.900.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7548,16 +7548,16 @@
         <v>170</v>
       </c>
       <c r="D39" t="n">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp13.629.000</t>
+          <t>Rp13.979.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>64</v>
       </c>
       <c r="D42" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp3.150.000</t>
+          <t>Rp3.300.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -8002,16 +8002,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp15.240.000</t>
+          <t>Rp15.390.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8281,16 +8281,16 @@
         <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp9.265.000</t>
+          <t>Rp9.765.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8529,16 +8529,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp5.370.000</t>
+          <t>Rp5.180.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -9087,16 +9087,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp3.645.000</t>
+          <t>Rp3.780.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9211,16 +9211,16 @@
         <v>68</v>
       </c>
       <c r="D42" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp2.880.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-04.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-04.xlsx
@@ -544,16 +544,16 @@
         <v>144</v>
       </c>
       <c r="D4" t="n">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp12.000.000</t>
+          <t>Rp13.400.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp3.564.000</t>
+          <t>Rp3.465.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -606,16 +606,16 @@
         <v>34</v>
       </c>
       <c r="D6" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp1.250.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -792,16 +792,16 @@
         <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp10.570.000</t>
+          <t>Rp10.820.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>32.8%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp12.508.000</t>
+          <t>Rp13.470.500</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp5.100.000</t>
+          <t>Rp6.000.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1381,16 +1381,16 @@
         <v>68</v>
       </c>
       <c r="D31" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp5.253.000</t>
+          <t>Rp5.613.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1412,16 +1412,16 @@
         <v>64</v>
       </c>
       <c r="D32" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp1.741.000</t>
+          <t>Rp2.141.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1474,16 +1474,16 @@
         <v>68</v>
       </c>
       <c r="D34" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>20.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp2.240.000</t>
+          <t>Rp2.720.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp3.462.000</t>
+          <t>Rp3.854.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>68</v>
       </c>
       <c r="D36" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp3.300.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1691,16 +1691,16 @@
         <v>54</v>
       </c>
       <c r="D41" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp2.061.000</t>
+          <t>Rp2.259.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1877,16 +1877,16 @@
         <v>54</v>
       </c>
       <c r="D47" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp1.000.000</t>
+          <t>Rp1.100.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -1908,16 +1908,16 @@
         <v>96</v>
       </c>
       <c r="D48" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>44.8%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp7.117.000</t>
+          <t>Rp7.271.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2094,16 +2094,16 @@
         <v>60</v>
       </c>
       <c r="D54" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp145.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2187,16 +2187,16 @@
         <v>48</v>
       </c>
       <c r="D57" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp2.260.000</t>
+          <t>Rp2.380.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>32</v>
       </c>
       <c r="D59" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp2.475.000</t>
+          <t>Rp2.700.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>90</v>
       </c>
       <c r="D62" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp1.272.000</t>
+          <t>Rp1.472.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2373,16 +2373,16 @@
         <v>72</v>
       </c>
       <c r="D63" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp2.613.000</t>
+          <t>Rp2.873.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp2.365.000</t>
+          <t>Rp2.270.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2776,16 +2776,16 @@
         <v>98</v>
       </c>
       <c r="D76" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>17.3%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp2.620.000</t>
+          <t>Rp3.070.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>120</v>
       </c>
       <c r="D78" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp14.375.000</t>
+          <t>Rp14.865.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2993,16 +2993,16 @@
         <v>36</v>
       </c>
       <c r="D83" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp700.000</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3086,16 +3086,16 @@
         <v>96</v>
       </c>
       <c r="D86" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rp4.050.000</t>
+          <t>Rp4.650.000</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3427,16 +3427,16 @@
         <v>112</v>
       </c>
       <c r="D97" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>20.5%</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rp4.900.000</t>
+          <t>Rp5.100.000</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3602,16 +3602,16 @@
         <v>126</v>
       </c>
       <c r="D3" t="n">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp15.773.500</t>
+          <t>Rp16.653.500</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3633,16 +3633,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp4.668.000</t>
+          <t>Rp6.224.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3881,16 +3881,16 @@
         <v>51</v>
       </c>
       <c r="D12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp12.375.000</t>
+          <t>Rp11.585.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -3943,16 +3943,16 @@
         <v>70</v>
       </c>
       <c r="D14" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp2.796.000</t>
+          <t>Rp2.996.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>105</v>
       </c>
       <c r="D16" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>30.5%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp12.650.000</t>
+          <t>Rp13.000.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp7.380.000</t>
+          <t>Rp7.200.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4067,16 +4067,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp4.075.000</t>
+          <t>Rp4.775.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4129,16 +4129,16 @@
         <v>18</v>
       </c>
       <c r="D20" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp348.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -4222,16 +4222,16 @@
         <v>36</v>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp4.145.000</t>
+          <t>Rp4.405.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4501,16 +4501,16 @@
         <v>32</v>
       </c>
       <c r="D32" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp1.100.000</t>
+          <t>Rp1.300.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4532,16 +4532,16 @@
         <v>90</v>
       </c>
       <c r="D33" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp5.775.000</t>
+          <t>Rp6.100.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4656,16 +4656,16 @@
         <v>176</v>
       </c>
       <c r="D37" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp10.750.000</t>
+          <t>Rp11.050.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4842,16 +4842,16 @@
         <v>77</v>
       </c>
       <c r="D43" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp8.650.000</t>
+          <t>Rp9.300.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4997,16 +4997,16 @@
         <v>80</v>
       </c>
       <c r="D48" t="n">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp4.800.000</t>
+          <t>Rp5.400.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5028,16 +5028,16 @@
         <v>90</v>
       </c>
       <c r="D49" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp8.675.000</t>
+          <t>Rp9.125.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5059,16 +5059,16 @@
         <v>72</v>
       </c>
       <c r="D50" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp4.577.000</t>
+          <t>Rp4.975.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5245,16 +5245,16 @@
         <v>75</v>
       </c>
       <c r="D56" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp885.000</t>
+          <t>Rp958.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -5276,16 +5276,16 @@
         <v>51</v>
       </c>
       <c r="D57" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp1.750.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5307,16 +5307,16 @@
         <v>124</v>
       </c>
       <c r="D58" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp1.480.000</t>
+          <t>Rp1.440.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5369,16 +5369,16 @@
         <v>45</v>
       </c>
       <c r="D60" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp5.500.000</t>
+          <t>Rp6.000.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -5400,16 +5400,16 @@
         <v>36</v>
       </c>
       <c r="D61" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp2.600.000</t>
+          <t>Rp2.800.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -5493,16 +5493,16 @@
         <v>102</v>
       </c>
       <c r="D64" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp5.760.000</t>
+          <t>Rp5.040.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5555,16 +5555,16 @@
         <v>144</v>
       </c>
       <c r="D66" t="n">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp5.200.000</t>
+          <t>Rp5.800.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5648,16 +5648,16 @@
         <v>162</v>
       </c>
       <c r="D69" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp2.850.000</t>
+          <t>Rp3.300.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5792,16 +5792,16 @@
         <v>324</v>
       </c>
       <c r="D3" t="n">
-        <v>264</v>
+        <v>246</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp11.550.000</t>
+          <t>Rp15.015.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -5823,16 +5823,16 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp1.750.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -5854,16 +5854,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp9.500.000</t>
+          <t>Rp10.000.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -5916,16 +5916,16 @@
         <v>68</v>
       </c>
       <c r="D7" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp320.000</t>
+          <t>Rp400.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>27.0%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp22.300.000</t>
+          <t>Rp23.100.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp4.550.000</t>
+          <t>Rp5.800.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6009,16 +6009,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp5.850.000</t>
+          <t>Rp6.525.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp199.000</t>
+          <t>Rp796.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6195,16 +6195,16 @@
         <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp3.150.000</t>
+          <t>Rp3.850.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6226,16 +6226,16 @@
         <v>34</v>
       </c>
       <c r="D17" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp450.000</t>
+          <t>Rp650.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6288,16 +6288,16 @@
         <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp376.000</t>
+          <t>Rp1.128.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6463,16 +6463,16 @@
         <v>74</v>
       </c>
       <c r="D4" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp11.170.000</t>
+          <t>Rp12.365.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6556,16 +6556,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.100.000</t>
+          <t>Rp1.650.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>60</v>
       </c>
       <c r="D10" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp2.100.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6680,16 +6680,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp18.715.000</t>
+          <t>Rp19.055.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6773,16 +6773,16 @@
         <v>144</v>
       </c>
       <c r="D14" t="n">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>53.5%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp14.775.000</t>
+          <t>Rp16.525.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp3.800.000</t>
+          <t>Rp4.075.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6897,16 +6897,16 @@
         <v>90</v>
       </c>
       <c r="D18" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp600.000</t>
+          <t>Rp1.900.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>48</v>
       </c>
       <c r="D19" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp2.781.000</t>
+          <t>Rp3.079.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp5.913.000</t>
+          <t>Rp5.670.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7083,16 +7083,16 @@
         <v>16</v>
       </c>
       <c r="D24" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp480.000</t>
+          <t>Rp800.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -7207,16 +7207,16 @@
         <v>64</v>
       </c>
       <c r="D28" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp975.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -7371,7 +7371,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp15.200.000</t>
+          <t>Rp14.600.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7424,16 +7424,16 @@
         <v>108</v>
       </c>
       <c r="D35" t="n">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp745.000</t>
+          <t>Rp1.341.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7455,16 +7455,16 @@
         <v>180</v>
       </c>
       <c r="D36" t="n">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp3.675.000</t>
+          <t>Rp4.025.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7548,16 +7548,16 @@
         <v>170</v>
       </c>
       <c r="D39" t="n">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp13.979.000</t>
+          <t>Rp15.525.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7610,16 +7610,16 @@
         <v>80</v>
       </c>
       <c r="D41" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>7.5%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp800.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7703,16 +7703,16 @@
         <v>174</v>
       </c>
       <c r="D44" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp24.700.000</t>
+          <t>Rp25.300.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -7796,16 +7796,16 @@
         <v>108</v>
       </c>
       <c r="D47" t="n">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp3.250.000</t>
+          <t>Rp3.900.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -7858,16 +7858,16 @@
         <v>144</v>
       </c>
       <c r="D49" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp1.950.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -8002,16 +8002,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp15.390.000</t>
+          <t>Rp14.390.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8033,16 +8033,16 @@
         <v>34</v>
       </c>
       <c r="D4" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp1.670.000</t>
+          <t>Rp1.970.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -8064,16 +8064,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp6.250.000</t>
+          <t>Rp7.750.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8157,16 +8157,16 @@
         <v>54</v>
       </c>
       <c r="D8" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp300.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8281,16 +8281,16 @@
         <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp9.765.000</t>
+          <t>Rp10.650.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8343,16 +8343,16 @@
         <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp5.500.000</t>
+          <t>Rp6.000.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp808.500</t>
+          <t>Rp1.386.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8498,16 +8498,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp2.280.000</t>
+          <t>Rp2.470.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8529,16 +8529,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>60.4%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp5.180.000</t>
+          <t>Rp6.775.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>102</v>
       </c>
       <c r="D21" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp17.750.000</t>
+          <t>Rp18.550.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8622,16 +8622,16 @@
         <v>68</v>
       </c>
       <c r="D23" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp2.025.000</t>
+          <t>Rp3.150.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp6.090.000</t>
+          <t>Rp6.930.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp4.199.979</t>
+          <t>Rp4.799.976</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8808,16 +8808,16 @@
         <v>45</v>
       </c>
       <c r="D29" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp2.025.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -8839,16 +8839,16 @@
         <v>32</v>
       </c>
       <c r="D30" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>81.2%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp3.750.000</t>
+          <t>Rp4.050.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -8901,16 +8901,16 @@
         <v>54</v>
       </c>
       <c r="D32" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp3.185.000</t>
+          <t>Rp4.900.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -8994,16 +8994,16 @@
         <v>36</v>
       </c>
       <c r="D35" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp3.185.000</t>
+          <t>Rp3.460.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9087,16 +9087,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp3.780.000</t>
+          <t>Rp4.185.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp6.550.000</t>
+          <t>Rp6.150.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -9149,16 +9149,16 @@
         <v>64</v>
       </c>
       <c r="D40" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp2.873.000</t>
+          <t>Rp3.211.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -9242,16 +9242,16 @@
         <v>64</v>
       </c>
       <c r="D43" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>26.6%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp3.290.000</t>
+          <t>Rp3.800.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-04.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-04.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.260.000</t>
+          <t>Rp1.670.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -513,16 +513,16 @@
         <v>68</v>
       </c>
       <c r="D3" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp1.400.000</t>
+          <t>Rp1.600.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -606,16 +606,16 @@
         <v>34</v>
       </c>
       <c r="D6" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp3.500.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -761,16 +761,16 @@
         <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp3.800.000</t>
+          <t>Rp2.900.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -792,16 +792,16 @@
         <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp10.820.000</t>
+          <t>Rp11.480.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -916,16 +916,16 @@
         <v>112</v>
       </c>
       <c r="D16" t="n">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>22.3%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp4.220.000</t>
+          <t>Rp4.540.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>108</v>
       </c>
       <c r="D19" t="n">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.670.000</t>
+          <t>Rp2.440.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>102</v>
       </c>
       <c r="D23" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp3.750.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>64</v>
       </c>
       <c r="D25" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp3.225.000</t>
+          <t>Rp3.625.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.141.000</t>
+          <t>Rp1.861.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>68</v>
       </c>
       <c r="D36" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp3.300.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>72</v>
       </c>
       <c r="D37" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp3.160.000</t>
+          <t>Rp3.540.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1598,16 +1598,16 @@
         <v>64</v>
       </c>
       <c r="D38" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>32.8%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp3.580.000</t>
+          <t>Rp3.759.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1660,16 +1660,16 @@
         <v>72</v>
       </c>
       <c r="D40" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp600.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>51</v>
       </c>
       <c r="D42" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp2.025.000</t>
+          <t>Rp1.080.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1753,16 +1753,16 @@
         <v>234</v>
       </c>
       <c r="D43" t="n">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp6.969.000</t>
+          <t>Rp7.866.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>198</v>
       </c>
       <c r="D44" t="n">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp825.000</t>
+          <t>Rp1.725.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1815,16 +1815,16 @@
         <v>60</v>
       </c>
       <c r="D45" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp2.757.000</t>
+          <t>Rp2.967.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -1846,16 +1846,16 @@
         <v>45</v>
       </c>
       <c r="D46" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp800.000</t>
+          <t>Rp400.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -1908,16 +1908,16 @@
         <v>96</v>
       </c>
       <c r="D48" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp7.271.000</t>
+          <t>Rp7.425.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2032,16 +2032,16 @@
         <v>64</v>
       </c>
       <c r="D52" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp864.000</t>
+          <t>Rp2.016.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2094,16 +2094,16 @@
         <v>60</v>
       </c>
       <c r="D54" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp145.000</t>
+          <t>Rp270.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>32</v>
       </c>
       <c r="D59" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp2.925.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2342,16 +2342,16 @@
         <v>90</v>
       </c>
       <c r="D62" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rp1.472.000</t>
+          <t>Rp1.631.000</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2373,16 +2373,16 @@
         <v>72</v>
       </c>
       <c r="D63" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp2.873.000</t>
+          <t>Rp2.993.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -2404,16 +2404,16 @@
         <v>30</v>
       </c>
       <c r="D64" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp59.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -2497,16 +2497,16 @@
         <v>90</v>
       </c>
       <c r="D67" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp6.205.000</t>
+          <t>Rp6.803.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>128</v>
       </c>
       <c r="D70" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp5.574.000</t>
+          <t>Rp5.972.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2621,16 +2621,16 @@
         <v>96</v>
       </c>
       <c r="D71" t="n">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp150.000</t>
+          <t>Rp1.050.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>120</v>
       </c>
       <c r="D78" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp14.865.000</t>
+          <t>Rp15.110.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>108</v>
       </c>
       <c r="D79" t="n">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp2.350.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -2931,21 +2931,21 @@
         <v>85</v>
       </c>
       <c r="D81" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp1.781.000</t>
+          <t>Rp2.355.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Rp109.000 - Rp200.000</t>
+          <t>Rp99.000 - Rp200.000</t>
         </is>
       </c>
     </row>
@@ -2993,16 +2993,16 @@
         <v>36</v>
       </c>
       <c r="D83" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Rp700.000</t>
+          <t>Rp900.000</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3086,16 +3086,16 @@
         <v>96</v>
       </c>
       <c r="D86" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rp4.650.000</t>
+          <t>Rp5.250.000</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3117,16 +3117,16 @@
         <v>36</v>
       </c>
       <c r="D87" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp760.000</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3241,16 +3241,16 @@
         <v>119</v>
       </c>
       <c r="D91" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rp1.955.000</t>
+          <t>Rp2.135.000</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3365,16 +3365,16 @@
         <v>34</v>
       </c>
       <c r="D95" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rp2.250.000</t>
+          <t>Rp2.475.000</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -3427,16 +3427,16 @@
         <v>112</v>
       </c>
       <c r="D97" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rp5.100.000</t>
+          <t>Rp5.220.000</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -3571,16 +3571,16 @@
         <v>36</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.944.000</t>
+          <t>Rp2.187.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -3602,16 +3602,16 @@
         <v>126</v>
       </c>
       <c r="D3" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp16.653.500</t>
+          <t>Rp16.828.500</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3633,16 +3633,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp6.224.000</t>
+          <t>Rp7.002.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3695,16 +3695,16 @@
         <v>90</v>
       </c>
       <c r="D6" t="n">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>21.1%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp3.800.000</t>
+          <t>Rp5.000.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -3726,16 +3726,16 @@
         <v>162</v>
       </c>
       <c r="D7" t="n">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp3.800.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3788,16 +3788,16 @@
         <v>64</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>82.8%</t>
+          <t>81.2%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp3.250.000</t>
+          <t>Rp3.200.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>105</v>
       </c>
       <c r="D16" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>30.5%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp13.000.000</t>
+          <t>Rp13.900.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>65</v>
       </c>
       <c r="D17" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp7.200.000</t>
+          <t>Rp7.605.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -4377,16 +4377,16 @@
         <v>180</v>
       </c>
       <c r="D28" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp22.540.000</t>
+          <t>Rp22.785.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4532,16 +4532,16 @@
         <v>90</v>
       </c>
       <c r="D33" t="n">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp6.100.000</t>
+          <t>Rp7.675.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4656,16 +4656,16 @@
         <v>176</v>
       </c>
       <c r="D37" t="n">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp11.050.000</t>
+          <t>Rp8.000.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4718,16 +4718,16 @@
         <v>24</v>
       </c>
       <c r="D39" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp4.600.000</t>
+          <t>Rp4.000.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -4842,16 +4842,16 @@
         <v>77</v>
       </c>
       <c r="D43" t="n">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>26.0%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp9.300.000</t>
+          <t>Rp10.600.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4873,16 +4873,16 @@
         <v>54</v>
       </c>
       <c r="D44" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp1.750.000</t>
+          <t>Rp2.250.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -4966,16 +4966,16 @@
         <v>32</v>
       </c>
       <c r="D47" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp1.000.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -5028,16 +5028,16 @@
         <v>90</v>
       </c>
       <c r="D49" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp9.125.000</t>
+          <t>Rp9.650.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5059,16 +5059,16 @@
         <v>72</v>
       </c>
       <c r="D50" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp4.975.000</t>
+          <t>Rp5.373.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5090,16 +5090,16 @@
         <v>54</v>
       </c>
       <c r="D51" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp5.250.000</t>
+          <t>Rp5.500.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5183,16 +5183,16 @@
         <v>68</v>
       </c>
       <c r="D54" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp10.230.000</t>
+          <t>Rp9.570.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5245,16 +5245,16 @@
         <v>75</v>
       </c>
       <c r="D56" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp958.000</t>
+          <t>Rp1.056.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -5462,16 +5462,16 @@
         <v>90</v>
       </c>
       <c r="D63" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5493,16 +5493,16 @@
         <v>102</v>
       </c>
       <c r="D64" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp5.040.000</t>
+          <t>Rp5.310.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -5555,16 +5555,16 @@
         <v>144</v>
       </c>
       <c r="D66" t="n">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp5.800.000</t>
+          <t>Rp7.400.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5648,16 +5648,16 @@
         <v>162</v>
       </c>
       <c r="D69" t="n">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp3.300.000</t>
+          <t>Rp4.000.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5761,16 +5761,16 @@
         <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp160.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -5792,16 +5792,16 @@
         <v>324</v>
       </c>
       <c r="D3" t="n">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp15.015.000</t>
+          <t>Rp16.170.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -5823,16 +5823,16 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp2.500.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -5854,16 +5854,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp10.000.000</t>
+          <t>Rp11.250.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>256</v>
       </c>
       <c r="D8" t="n">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>27.0%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp23.100.000</t>
+          <t>Rp27.200.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6009,16 +6009,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.525.000</t>
+          <t>Rp6.975.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6040,16 +6040,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp796.000</t>
+          <t>Rp1.194.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>51</v>
       </c>
       <c r="D14" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>31.4%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp3.200.000</t>
+          <t>Rp3.800.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6164,16 +6164,16 @@
         <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.192.000</t>
+          <t>Rp3.696.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6257,16 +6257,16 @@
         <v>48</v>
       </c>
       <c r="D18" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp875.000</t>
+          <t>Rp1.025.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6401,16 +6401,16 @@
         <v>200</v>
       </c>
       <c r="D2" t="n">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>19.5%</t>
+          <t>21.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp13.370.000</t>
+          <t>Rp13.600.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6432,16 +6432,16 @@
         <v>86</v>
       </c>
       <c r="D3" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp9.350.000</t>
+          <t>Rp10.600.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp495.000</t>
+          <t>Rp694.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6525,16 +6525,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp16.595.000</t>
+          <t>Rp17.180.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6556,16 +6556,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>60</v>
       </c>
       <c r="D10" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6680,16 +6680,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp19.055.000</t>
+          <t>Rp19.735.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6773,16 +6773,16 @@
         <v>144</v>
       </c>
       <c r="D14" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp16.525.000</t>
+          <t>Rp17.125.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp4.075.000</t>
+          <t>Rp4.375.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6866,16 +6866,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp4.000.000</t>
+          <t>Rp4.200.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>48</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp3.079.000</t>
+          <t>Rp3.675.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp18.900.000</t>
+          <t>Rp20.300.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp5.670.000</t>
+          <t>Rp5.832.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7083,16 +7083,16 @@
         <v>16</v>
       </c>
       <c r="D24" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp800.000</t>
+          <t>Rp1.120.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -7114,16 +7114,16 @@
         <v>108</v>
       </c>
       <c r="D25" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp4.577.000</t>
+          <t>Rp5.373.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7176,16 +7176,16 @@
         <v>96</v>
       </c>
       <c r="D27" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp2.100.000</t>
+          <t>Rp2.350.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7235,14 +7235,14 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="D29" t="n">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -7252,7 +7252,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rp160.000 - Rp400.000</t>
+          <t>Rp90.000 - Rp400.000</t>
         </is>
       </c>
     </row>
@@ -7331,16 +7331,16 @@
         <v>108</v>
       </c>
       <c r="D32" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>187</v>
       </c>
       <c r="D33" t="n">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp14.600.000</t>
+          <t>Rp15.050.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7393,16 +7393,16 @@
         <v>72</v>
       </c>
       <c r="D34" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp1.692.000</t>
+          <t>Rp2.444.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7424,16 +7424,16 @@
         <v>108</v>
       </c>
       <c r="D35" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp1.341.000</t>
+          <t>Rp1.639.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7455,16 +7455,16 @@
         <v>180</v>
       </c>
       <c r="D36" t="n">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>16.1%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp4.025.000</t>
+          <t>Rp4.625.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -7548,16 +7548,16 @@
         <v>170</v>
       </c>
       <c r="D39" t="n">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp15.525.000</t>
+          <t>Rp16.772.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7579,16 +7579,16 @@
         <v>128</v>
       </c>
       <c r="D40" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>3.1%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp598.000</t>
+          <t>Rp1.196.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>64</v>
       </c>
       <c r="D42" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp3.300.000</t>
+          <t>Rp3.900.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -7734,16 +7734,16 @@
         <v>102</v>
       </c>
       <c r="D45" t="n">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp2.750.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -7796,16 +7796,16 @@
         <v>108</v>
       </c>
       <c r="D47" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp3.900.000</t>
+          <t>Rp4.550.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -7827,16 +7827,16 @@
         <v>102</v>
       </c>
       <c r="D48" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp5.100.000</t>
+          <t>Rp5.400.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -7889,16 +7889,16 @@
         <v>90</v>
       </c>
       <c r="D50" t="n">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp2.600.000</t>
+          <t>Rp3.200.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -7971,16 +7971,16 @@
         <v>72</v>
       </c>
       <c r="D2" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.908.000</t>
+          <t>Rp2.226.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -8002,16 +8002,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp14.390.000</t>
+          <t>Rp15.830.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -8064,16 +8064,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp7.750.000</t>
+          <t>Rp8.250.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8126,16 +8126,16 @@
         <v>48</v>
       </c>
       <c r="D7" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>77.1%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp6.590.000</t>
+          <t>Rp7.415.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -8157,16 +8157,16 @@
         <v>54</v>
       </c>
       <c r="D8" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>5.6%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp300.000</t>
+          <t>Rp485.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8219,16 +8219,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp5.850.000</t>
+          <t>Rp6.150.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8281,16 +8281,16 @@
         <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp10.650.000</t>
+          <t>Rp10.930.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8343,16 +8343,16 @@
         <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp6.000.000</t>
+          <t>Rp6.750.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp3.399.983</t>
+          <t>Rp3.999.980</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp300.000</t>
+          <t>Rp450.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp1.386.000</t>
+          <t>Rp2.310.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8467,16 +8467,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp2.550.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8498,16 +8498,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp2.470.000</t>
+          <t>Rp2.850.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8529,16 +8529,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>60.4%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp6.775.000</t>
+          <t>Rp6.170.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>102</v>
       </c>
       <c r="D21" t="n">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp18.550.000</t>
+          <t>Rp19.950.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp6.930.000</t>
+          <t>Rp6.090.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8684,16 +8684,16 @@
         <v>36</v>
       </c>
       <c r="D25" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp475.000</t>
+          <t>Rp913.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp4.799.976</t>
+          <t>Rp5.999.970</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8746,16 +8746,16 @@
         <v>54</v>
       </c>
       <c r="D27" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp2.250.000</t>
+          <t>Rp3.600.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -8777,16 +8777,16 @@
         <v>32</v>
       </c>
       <c r="D28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp2.275.000</t>
+          <t>Rp2.450.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>54</v>
       </c>
       <c r="D34" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp350.000</t>
+          <t>Rp700.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -8994,16 +8994,16 @@
         <v>36</v>
       </c>
       <c r="D35" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp3.460.000</t>
+          <t>Rp3.695.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>144</v>
       </c>
       <c r="D36" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>13.9%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp4.820.000</t>
+          <t>Rp3.980.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>51</v>
       </c>
       <c r="D37" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp1.295.000</t>
+          <t>Rp1.665.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -9087,16 +9087,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp4.185.000</t>
+          <t>Rp4.419.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp6.150.000</t>
+          <t>Rp6.700.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -9242,16 +9242,16 @@
         <v>64</v>
       </c>
       <c r="D43" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp3.800.000</t>
+          <t>Rp4.240.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-10-04.xlsx
+++ b/laporan_padel_dki_jakarta_2026-10-04.xlsx
@@ -513,16 +513,16 @@
         <v>68</v>
       </c>
       <c r="D3" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp6.000.000</t>
+          <t>Rp6.600.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp3.854.000</t>
+          <t>Rp3.952.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1877,16 +1877,16 @@
         <v>54</v>
       </c>
       <c r="D47" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp1.100.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2869,16 +2869,16 @@
         <v>108</v>
       </c>
       <c r="D79" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Rp2.350.000</t>
+          <t>Rp2.500.000</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -4532,16 +4532,16 @@
         <v>90</v>
       </c>
       <c r="D33" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp7.675.000</t>
+          <t>Rp7.525.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -5854,16 +5854,16 @@
         <v>102</v>
       </c>
       <c r="D5" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp11.250.000</t>
+          <t>Rp11.500.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6009,16 +6009,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.975.000</t>
+          <t>Rp7.200.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp694.000</t>
+          <t>Rp1.200.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6525,16 +6525,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp17.180.000</t>
+          <t>Rp17.570.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp4.375.000</t>
+          <t>Rp4.675.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>126</v>
       </c>
       <c r="D23" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp5.832.000</t>
+          <t>Rp5.913.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>187</v>
       </c>
       <c r="D33" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp15.050.000</t>
+          <t>Rp15.150.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7548,16 +7548,16 @@
         <v>170</v>
       </c>
       <c r="D39" t="n">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp16.772.000</t>
+          <t>Rp17.071.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7610,16 +7610,16 @@
         <v>80</v>
       </c>
       <c r="D41" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp800.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -8219,16 +8219,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.150.000</t>
+          <t>Rp6.300.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8281,16 +8281,16 @@
         <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp10.930.000</t>
+          <t>Rp11.330.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
